--- a/output/第10期計画_要介護認定データの確認.xlsx
+++ b/output/第10期計画_要介護認定データの確認.xlsx
@@ -628,7 +628,7 @@
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>令和8年8月4日に見える化システムのB系列27ファイルを受領しました。要介護度別の認定者数が令和8年3月末まで得られたため、資料依頼No.14（要介護度別認定者数の実績）は解消し、将来推計の第2段階（サービス見込量）の前提が整いました。あわせて、既存の記述との突合、新たに分かったこと、データの限界を整理しました。作成日：令和8年8月4日。</t>
+          <t>令和8年8月4日に見える化システムのB系列27ファイルを受領しました。要介護度別の認定者数が令和8年3月末まで得られたため、当初の資料依頼事項（要介護度別認定者数の実績）は解消し、将来推計の第2段階（サービス見込量）の前提が整いました。あわせて、既存の記述との突合、新たに分かったこと、データの限界を整理しました。作成日：令和8年8月4日。</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>令和8年3月末の合計1,984人は、将来推計で基準年度の実績として用いている値と一致します。要支援1 298人・要支援2 292人・要介護1 515人・要介護2 299人・要介護3 212人・要介護4 213人・要介護5 155人です。資料依頼No.14が求めていた「令和元年〜令和8年度・各年3月末」を上回る期間が得られました。</t>
+          <t>令和8年3月末の合計1,984人は、将来推計で基準年度の実績として用いている値と一致します。要支援1 298人・要支援2 292人・要介護1 515人・要介護2 299人・要介護3 212人・要介護4 213人・要介護5 155人です。当初の資料依頼事項が求めていた「令和元年〜令和8年度・各年3月末」を上回る期間が得られました。</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -960,7 +960,7 @@
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>各年3月末時点。第1号被保険者のみ（第2号被保険者を含まない）。資料依頼No.14が求めていた要介護度別認定者数に相当する。</t>
+          <t>各年3月末時点。第1号被保険者のみ（第2号被保険者を含まない）。当初の資料依頼事項が求めていた要介護度別認定者数に相当する。</t>
         </is>
       </c>
     </row>
@@ -5231,7 +5231,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>資料依頼No.14は解消します。第2段階の着手には、要介護度別・サービス種別の受給者数が別途必要である旨を必要事項の一覧に追加します。</t>
+          <t>当該資料依頼事項は解消します。第2段階の着手には、要介護度別・サービス種別の受給者数が別途必要である旨を必要事項の一覧に追加します。</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">

--- a/output/第10期計画_要介護認定データの確認.xlsx
+++ b/output/第10期計画_要介護認定データの確認.xlsx
@@ -705,7 +705,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>調整済み重度認定率は平成30年3月末5.4％から令和7年3月末4.7％へ低下が続き、調整済み軽度認定率は令和5年3月末11.7％を底に令和7年3月末12.0％へ上昇しています。レッドチームレビューNo.1で訂正した内容が原典で確認できました。</t>
+          <t>調整済み重度認定率は平成30年3月末5.4％から令和7年3月末4.7％へ低下が続き、調整済み軽度認定率は令和5年3月末11.7％を底に令和7年3月末12.0％へ上昇しています。自己点検記録No.1で訂正した内容が原典で確認できました。</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -2788,7 +2788,7 @@
     <row r="26" ht="104" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>注1）調整済み認定率には2系列があり、令和7年3月末で【注目する地域のみ】18.4％、【他地域と比較】16.7％と値が異なる。18.4％は当広域連合のみを対象に標準化した値であり、全国・北海道と比較できない。第4章のH01でこの18.4％を撤回し見える化W144に改めた判断は、原典により裏付けられた。他地域と比較する場合は【他地域と比較】系列（16.7％）を用いる。注2）調整済み重度認定率は平成30年3月末5.4％から令和7年3月末4.7％へ一貫して低下している。調整済み軽度認定率は令和5年3月末11.7％を底に令和7年3月末12.0％へ上昇しており、レッドチームレビューNo.1の訂正のとおりである。注3）認定率は令和元年3月末20.3％から令和8年3月末21.8％へ1.5ポイント上昇したが、年齢構成を調整すると17.2％（令和元年）から16.7％（令和7年）へ低下している。認定率の上昇は高齢化によるものである。</t>
+          <t>注1）調整済み認定率には2系列があり、令和7年3月末で【注目する地域のみ】18.4％、【他地域と比較】16.7％と値が異なる。18.4％は当広域連合のみを対象に標準化した値であり、全国・北海道と比較できない。第4章のH01でこの18.4％を撤回し見える化W144に改めた判断は、原典により裏付けられた。他地域と比較する場合は【他地域と比較】系列（16.7％）を用いる。注2）調整済み重度認定率は平成30年3月末5.4％から令和7年3月末4.7％へ一貫して低下している。調整済み軽度認定率は令和5年3月末11.7％を底に令和7年3月末12.0％へ上昇しており、自己点検記録No.1の訂正のとおりである。注3）認定率は令和元年3月末20.3％から令和8年3月末21.8％へ1.5ポイント上昇したが、年齢構成を調整すると17.2％（令和元年）から16.7％（令和7年）へ低下している。認定率の上昇は高齢化によるものである。</t>
         </is>
       </c>
     </row>
@@ -5046,7 +5046,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>第2章第2節　調整済み重度認定率は5.4％から4.7％へ低下が続き、調整済み軽度認定率は令和5年11.7％を底に令和7年12.0％へ上昇（レッドチームレビューNo.1で訂正）</t>
+          <t>第2章第2節　調整済み重度認定率は5.4％から4.7％へ低下が続き、調整済み軽度認定率は令和5年11.7％を底に令和7年12.0％へ上昇（自己点検記録No.1で訂正）</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>第9期計画及び計画素案第10稿には認知症高齢者自立度の系列を用いた記述がありません。B7により平成24年から令和6年までの26時点が得られました。</t>
+          <t>第9期計画及び計画素案には認知症高齢者自立度の系列を用いた記述がありません。B7により平成24年から令和6年までの26時点が得られました。</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">

--- a/output/第10期計画_要介護認定データの確認.xlsx
+++ b/output/第10期計画_要介護認定データの確認.xlsx
@@ -705,7 +705,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>調整済み重度認定率は平成30年3月末5.4％から令和7年3月末4.7％へ低下が続き、調整済み軽度認定率は令和5年3月末11.7％を底に令和7年3月末12.0％へ上昇しています。自己点検記録No.1で訂正した内容が原典で確認できました。</t>
+          <t>調整済み重度認定率は平成30年3月末5.4％から令和7年3月末4.7％へ低下が続き、調整済み軽度認定率は令和5年3月末11.7％を底に令和7年3月末12.0％へ上昇しています。受託者の自己点検で訂正した内容が原典で確認できました。</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -2788,7 +2788,7 @@
     <row r="26" ht="104" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>注1）調整済み認定率には2系列があり、令和7年3月末で【注目する地域のみ】18.4％、【他地域と比較】16.7％と値が異なる。18.4％は当広域連合のみを対象に標準化した値であり、全国・北海道と比較できない。第4章のH01でこの18.4％を撤回し見える化W144に改めた判断は、原典により裏付けられた。他地域と比較する場合は【他地域と比較】系列（16.7％）を用いる。注2）調整済み重度認定率は平成30年3月末5.4％から令和7年3月末4.7％へ一貫して低下している。調整済み軽度認定率は令和5年3月末11.7％を底に令和7年3月末12.0％へ上昇しており、自己点検記録No.1の訂正のとおりである。注3）認定率は令和元年3月末20.3％から令和8年3月末21.8％へ1.5ポイント上昇したが、年齢構成を調整すると17.2％（令和元年）から16.7％（令和7年）へ低下している。認定率の上昇は高齢化によるものである。</t>
+          <t>注1）調整済み認定率には2系列があり、令和7年3月末で【注目する地域のみ】18.4％、【他地域と比較】16.7％と値が異なる。18.4％は当広域連合のみを対象に標準化した値であり、全国・北海道と比較できない。第4章のH01でこの18.4％を撤回し見える化W144に改めた判断は、原典により裏付けられた。他地域と比較する場合は【他地域と比較】系列（16.7％）を用いる。注2）調整済み重度認定率は平成30年3月末5.4％から令和7年3月末4.7％へ一貫して低下している。調整済み軽度認定率は令和5年3月末11.7％を底に令和7年3月末12.0％へ上昇しており、受託者の自己点検の訂正のとおりである。注3）認定率は令和元年3月末20.3％から令和8年3月末21.8％へ1.5ポイント上昇したが、年齢構成を調整すると17.2％（令和元年）から16.7％（令和7年）へ低下している。認定率の上昇は高齢化によるものである。</t>
         </is>
       </c>
     </row>
@@ -5046,7 +5046,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>第2章第2節　調整済み重度認定率は5.4％から4.7％へ低下が続き、調整済み軽度認定率は令和5年11.7％を底に令和7年12.0％へ上昇（自己点検記録No.1で訂正）</t>
+          <t>第2章第2節　調整済み重度認定率は5.4％から4.7％へ低下が続き、調整済み軽度認定率は令和5年11.7％を底に令和7年12.0％へ上昇（受託者の自己点検で訂正）</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
